--- a/Practicas/Practica 7/Matriz de riegos 1.xlsx
+++ b/Practicas/Practica 7/Matriz de riegos 1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ciencias\CalidadSofwtareBSPO\Practicas\Practica 7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F3219EC-711C-4B00-A721-77E8E0E6BB40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F04B12F6-ABDF-4136-9265-CE23490770D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="67">
   <si>
     <t>Menor</t>
   </si>
@@ -254,12 +254,42 @@
   <si>
     <t xml:space="preserve"> Extremo</t>
   </si>
+  <si>
+    <t>Fallo en descarga de archivos (export chat)</t>
+  </si>
+  <si>
+    <t>R11</t>
+  </si>
+  <si>
+    <t>R12</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
+    <t>R14</t>
+  </si>
+  <si>
+    <t>R15</t>
+  </si>
+  <si>
+    <t>Ingreso de datos inválidos por el usuario en variables del prompt</t>
+  </si>
+  <si>
+    <t>Uso incorrecto de parámetros del modelo (temperature, top_p, etc.)</t>
+  </si>
+  <si>
+    <t>Interfaz poco intuitiva para completar templates</t>
+  </si>
+  <si>
+    <t>Generación de prompts ambiguos o mal estructurados</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -326,6 +356,12 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="10">
@@ -566,13 +602,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -584,17 +620,17 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1053,42 +1089,42 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="26"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
+      <c r="A13" s="35"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="26"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
+      <c r="A14" s="35"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="26"/>
-      <c r="B15" s="26"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
+      <c r="A15" s="35"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="25"/>
@@ -1124,23 +1160,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
     </row>
     <row r="2" spans="2:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
       <c r="E3" s="29" t="s">
@@ -1190,19 +1226,19 @@
       <c r="K5" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="L5" s="32" t="s">
+      <c r="L5" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="M5" s="32"/>
-      <c r="N5" s="32"/>
-      <c r="O5" s="32"/>
-      <c r="P5" s="32"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
       <c r="Q5" s="21" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="32" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="18" t="s">
@@ -1237,7 +1273,7 @@
       <c r="Q6" s="8"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B7" s="33"/>
+      <c r="B7" s="32"/>
       <c r="C7" s="18" t="s">
         <v>11</v>
       </c>
@@ -1270,7 +1306,7 @@
       <c r="Q7" s="2"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B8" s="33"/>
+      <c r="B8" s="32"/>
       <c r="C8" s="18" t="s">
         <v>14</v>
       </c>
@@ -1303,7 +1339,7 @@
       <c r="Q8" s="3"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B9" s="33"/>
+      <c r="B9" s="32"/>
       <c r="C9" s="18" t="s">
         <v>12</v>
       </c>
@@ -1336,7 +1372,7 @@
       <c r="Q9" s="9"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B10" s="33"/>
+      <c r="B10" s="32"/>
       <c r="C10" s="18" t="s">
         <v>13</v>
       </c>
@@ -1400,7 +1436,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="B1:Q24"/>
+  <dimension ref="B1:Q29"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.7109375" customWidth="1"/>
@@ -1418,23 +1454,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
     </row>
     <row r="2" spans="2:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
       <c r="E3" s="29" t="s">
@@ -1484,19 +1520,19 @@
       <c r="K5" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="L5" s="32" t="s">
+      <c r="L5" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="M5" s="32"/>
-      <c r="N5" s="32"/>
-      <c r="O5" s="32"/>
-      <c r="P5" s="32"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
       <c r="Q5" s="21" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="32" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="18" t="s">
@@ -1546,7 +1582,7 @@
       <c r="Q6" s="8"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B7" s="33"/>
+      <c r="B7" s="32"/>
       <c r="C7" s="18" t="s">
         <v>11</v>
       </c>
@@ -1594,7 +1630,7 @@
       <c r="Q7" s="2"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B8" s="33"/>
+      <c r="B8" s="32"/>
       <c r="C8" s="18" t="s">
         <v>14</v>
       </c>
@@ -1642,7 +1678,7 @@
       <c r="Q8" s="3"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B9" s="33"/>
+      <c r="B9" s="32"/>
       <c r="C9" s="18" t="s">
         <v>12</v>
       </c>
@@ -1690,7 +1726,7 @@
       <c r="Q9" s="9"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B10" s="33"/>
+      <c r="B10" s="32"/>
       <c r="C10" s="18" t="s">
         <v>13</v>
       </c>
@@ -1746,27 +1782,27 @@
       <c r="L14" s="7"/>
     </row>
     <row r="15" spans="2:17" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="D15" s="35" t="s">
+      <c r="D15" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="35" t="s">
+      <c r="E15" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="34" t="s">
+      <c r="F15" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="G15" s="34">
+      <c r="G15" s="26">
         <f>VLOOKUP(F15,$C$6:$D$10,2,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="H15" s="34" t="s">
+      <c r="H15" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="I15" s="34">
+      <c r="I15" s="26">
         <f>HLOOKUP(H15,$E$4:$I$5,2,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="J15" s="34">
+      <c r="J15" s="26">
         <f>+G15*I15</f>
         <v>9</v>
       </c>
@@ -1776,27 +1812,27 @@
       </c>
     </row>
     <row r="16" spans="2:17" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="D16" s="35" t="s">
+      <c r="D16" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="E16" s="35" t="s">
+      <c r="E16" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="34" t="s">
+      <c r="F16" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="34">
+      <c r="G16" s="26">
         <f t="shared" ref="G16:G24" si="2">VLOOKUP(F16,$C$6:$D$10,2,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="H16" s="34" t="s">
+      <c r="H16" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="I16" s="34">
+      <c r="I16" s="26">
         <f t="shared" ref="I16:I24" si="3">HLOOKUP(H16,$E$4:$I$5,2,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="J16" s="34">
+      <c r="J16" s="26">
         <f t="shared" ref="J16:J24" si="4">+G16*I16</f>
         <v>4</v>
       </c>
@@ -1806,27 +1842,27 @@
       </c>
     </row>
     <row r="17" spans="4:11" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="D17" s="35" t="s">
+      <c r="D17" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="E17" s="35" t="s">
+      <c r="E17" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="34" t="s">
+      <c r="F17" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="G17" s="34">
+      <c r="G17" s="26">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="H17" s="34" t="s">
+      <c r="H17" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="I17" s="34">
+      <c r="I17" s="26">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="J17" s="34">
+      <c r="J17" s="26">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
@@ -1836,27 +1872,27 @@
       </c>
     </row>
     <row r="18" spans="4:11" ht="39" x14ac:dyDescent="0.25">
-      <c r="D18" s="35" t="s">
+      <c r="D18" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="E18" s="35" t="s">
+      <c r="E18" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="F18" s="34" t="s">
+      <c r="F18" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="G18" s="34">
+      <c r="G18" s="26">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="H18" s="34" t="s">
+      <c r="H18" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="I18" s="34">
+      <c r="I18" s="26">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="J18" s="34">
+      <c r="J18" s="26">
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
@@ -1866,27 +1902,27 @@
       </c>
     </row>
     <row r="19" spans="4:11" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="D19" s="35" t="s">
+      <c r="D19" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="E19" s="35" t="s">
+      <c r="E19" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="F19" s="34" t="s">
+      <c r="F19" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="G19" s="34">
+      <c r="G19" s="26">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="H19" s="34" t="s">
+      <c r="H19" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="I19" s="34">
+      <c r="I19" s="26">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="J19" s="34">
+      <c r="J19" s="26">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
@@ -1896,27 +1932,27 @@
       </c>
     </row>
     <row r="20" spans="4:11" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="D20" s="35" t="s">
+      <c r="D20" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="E20" s="35" t="s">
+      <c r="E20" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="F20" s="34" t="s">
+      <c r="F20" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="34">
+      <c r="G20" s="26">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="H20" s="34" t="s">
+      <c r="H20" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="I20" s="34">
+      <c r="I20" s="26">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="J20" s="34">
+      <c r="J20" s="26">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
@@ -1926,27 +1962,27 @@
       </c>
     </row>
     <row r="21" spans="4:11" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="D21" s="35" t="s">
+      <c r="D21" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="E21" s="35" t="s">
+      <c r="E21" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="F21" s="34" t="s">
+      <c r="F21" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="G21" s="34">
+      <c r="G21" s="26">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="H21" s="34" t="s">
+      <c r="H21" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="I21" s="34">
+      <c r="I21" s="26">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="J21" s="34">
+      <c r="J21" s="26">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
@@ -1956,27 +1992,27 @@
       </c>
     </row>
     <row r="22" spans="4:11" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="D22" s="35" t="s">
+      <c r="D22" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="35" t="s">
+      <c r="E22" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="34" t="s">
+      <c r="F22" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="G22" s="34">
+      <c r="G22" s="26">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="H22" s="34" t="s">
+      <c r="H22" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="I22" s="34">
+      <c r="I22" s="26">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="J22" s="34">
+      <c r="J22" s="26">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
@@ -1986,27 +2022,27 @@
       </c>
     </row>
     <row r="23" spans="4:11" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="D23" s="35" t="s">
+      <c r="D23" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="E23" s="35" t="s">
+      <c r="E23" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="F23" s="34" t="s">
+      <c r="F23" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="G23" s="34">
+      <c r="G23" s="26">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="H23" s="34" t="s">
+      <c r="H23" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="I23" s="34">
+      <c r="I23" s="26">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="J23" s="34">
+      <c r="J23" s="26">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
@@ -2016,32 +2052,176 @@
       </c>
     </row>
     <row r="24" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D24" s="35" t="s">
+      <c r="D24" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="E24" s="35" t="s">
+      <c r="E24" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="F24" s="34" t="s">
+      <c r="F24" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="G24" s="34">
+      <c r="G24" s="26">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="H24" s="34" t="s">
+      <c r="H24" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="I24" s="34">
+      <c r="I24" s="26">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="J24" s="34">
+      <c r="J24" s="26">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="K24" s="6" t="str">
         <f t="shared" si="5"/>
+        <v xml:space="preserve"> Aceptable</v>
+      </c>
+    </row>
+    <row r="25" spans="4:11" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="D25" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="E25" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" s="26">
+        <v>1</v>
+      </c>
+      <c r="H25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="I25" s="26">
+        <f t="shared" ref="I25" si="6">HLOOKUP(H25,$E$4:$I$5,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="J25" s="26">
+        <f t="shared" ref="J25" si="7">+G25*I25</f>
+        <v>3</v>
+      </c>
+      <c r="K25" s="6" t="str">
+        <f t="shared" ref="K25" si="8">IF(J25&gt;=17,$K$9,IF(J25&gt;=11,$K$8,IF(J25&gt;=5,$K$7,IF(J25&gt;=1,$K$6,0))))</f>
+        <v xml:space="preserve"> Aceptable</v>
+      </c>
+    </row>
+    <row r="26" spans="4:11" ht="39" x14ac:dyDescent="0.25">
+      <c r="D26" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="F26" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="26">
+        <v>1</v>
+      </c>
+      <c r="H26" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="26">
+        <f t="shared" ref="I26:I29" si="9">HLOOKUP(H26,$E$4:$I$5,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="J26" s="26">
+        <f t="shared" ref="J26:J29" si="10">+G26*I26</f>
+        <v>3</v>
+      </c>
+      <c r="K26" s="6" t="str">
+        <f t="shared" ref="K26:K29" si="11">IF(J26&gt;=17,$K$9,IF(J26&gt;=11,$K$8,IF(J26&gt;=5,$K$7,IF(J26&gt;=1,$K$6,0))))</f>
+        <v xml:space="preserve"> Aceptable</v>
+      </c>
+    </row>
+    <row r="27" spans="4:11" ht="39" x14ac:dyDescent="0.25">
+      <c r="D27" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="E27" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="F27" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" s="26">
+        <v>2</v>
+      </c>
+      <c r="H27" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="I27" s="26">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="J27" s="26">
+        <f t="shared" si="10"/>
+        <v>4</v>
+      </c>
+      <c r="K27" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve"> Aceptable</v>
+      </c>
+    </row>
+    <row r="28" spans="4:11" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="D28" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="E28" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F28" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" s="26">
+        <v>1</v>
+      </c>
+      <c r="H28" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="I28" s="26">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="J28" s="26">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="K28" s="6" t="str">
+        <f t="shared" si="11"/>
+        <v xml:space="preserve"> Aceptable</v>
+      </c>
+    </row>
+    <row r="29" spans="4:11" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="D29" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="E29" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="F29" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" s="26">
+        <v>2</v>
+      </c>
+      <c r="H29" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="26">
+        <v>2</v>
+      </c>
+      <c r="J29" s="26">
+        <f t="shared" si="10"/>
+        <v>4</v>
+      </c>
+      <c r="K29" s="6" t="str">
+        <f t="shared" si="11"/>
         <v xml:space="preserve"> Aceptable</v>
       </c>
     </row>
@@ -2053,11 +2233,12 @@
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="E2:I2"/>
   </mergeCells>
+  <phoneticPr fontId="9" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F24" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F29" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>$C$6:$C$10</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15:H24" xr:uid="{00000000-0002-0000-0200-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H15:H29" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>$E$4:$I$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -2129,7 +2310,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>K15:K24</xm:sqref>
+          <xm:sqref>K15:K29</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
